--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>table</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>patron_hands_per_hour</t>
+  </si>
+  <si>
+    <t>available_from</t>
+  </si>
+  <si>
+    <t>available_to</t>
   </si>
   <si>
     <t>T00</t>
@@ -110,6 +116,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -162,11 +171,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,10 +471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,13 +490,19 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -497,13 +513,16 @@
       <c r="E2">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="G2" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>24</v>
@@ -515,12 +534,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>24</v>
@@ -532,12 +551,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>24</v>
@@ -549,12 +568,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -566,12 +585,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -583,12 +602,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -600,12 +619,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -617,12 +636,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>16</v>
@@ -634,12 +653,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -651,12 +670,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>16</v>
@@ -668,12 +687,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -685,12 +704,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -702,12 +721,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -719,12 +738,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>8</v>
@@ -736,12 +755,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -753,12 +772,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -770,12 +789,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -787,12 +806,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -804,21 +823,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
-      <c r="D21">
-        <v>68</v>
-      </c>
-      <c r="E21">
-        <v>53</v>
+      <c r="F21" s="2">
+        <v>46267</v>
       </c>
     </row>
   </sheetData>
